--- a/app/src/main/java/com/example/methodmesh/modules/magnifier/docs/example_odk_showcase_visual_magnifier_capture.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/magnifier/docs/example_odk_showcase_visual_magnifier_capture.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rab3054884c8c4525"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R630c2cd679684666"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rb319f7e38bf24944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R045bb6ccc0994c96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Ree4048c7db754fa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rca4fa8b9edd04b49"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +26,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -35,7 +35,22 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE2E8F0"/>
+        <x:fgColor rgb="FFE8EEF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EEF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EEF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EEF7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -46,24 +61,43 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -267,309 +301,237 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>type</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>label</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="str">
-        <x:v>hint</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>appearance</x:v>
       </x:c>
-      <x:c r="F1" s="4" t="str">
-        <x:v>required</x:v>
-      </x:c>
-      <x:c r="G1" s="4" t="str">
-        <x:v>relevant</x:v>
-      </x:c>
-      <x:c r="H1" s="4" t="str">
-        <x:v>constraint</x:v>
-      </x:c>
-      <x:c r="I1" s="4" t="str">
-        <x:v>constraint_message</x:v>
-      </x:c>
-      <x:c r="J1" s="4" t="str">
-        <x:v>calculation</x:v>
-      </x:c>
-      <x:c r="K1" s="4" t="str">
-        <x:v>default</x:v>
-      </x:c>
-      <x:c r="L1" s="4" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>read_only</x:v>
       </x:c>
-      <x:c r="M1" s="4" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>body::intent</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="8" t="str">
-        <x:v>note</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="str">
-        <x:v>intro</x:v>
-      </x:c>
-      <x:c r="C2" s="8" t="str">
-        <x:v>MethodMesh Magnifier — visual.magnifier.capture</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="str">
-        <x:v>Dedicated MethodMesh capability showcase.</x:v>
-      </x:c>
-      <x:c r="E2" s="8" t="str"/>
-      <x:c r="F2" s="8" t="str"/>
-      <x:c r="G2" s="8" t="str"/>
-      <x:c r="H2" s="8" t="str"/>
-      <x:c r="I2" s="8" t="str"/>
-      <x:c r="J2" s="8" t="str"/>
-      <x:c r="K2" s="8" t="str"/>
-      <x:c r="L2" s="8" t="str"/>
-      <x:c r="M2" s="8" t="str"/>
+      <x:c r="A2" s="9" t="str">
+        <x:v>select_one magnifier_camera</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>camera_facing</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>Camera</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>minimal</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str"/>
+      <x:c r="F2" s="9" t="str"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="8" t="str">
+      <x:c r="A3" s="9" t="str">
+        <x:v>select_one magnifier_light</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="str">
+        <x:v>default_light</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>Starting light</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="str">
+        <x:v>minimal</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="str"/>
+      <x:c r="F3" s="9" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>select_one magnifier_filter</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>default_filter</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>Starting live filter</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>minimal</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str"/>
+      <x:c r="F4" s="9" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
         <x:v>begin_group</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
-        <x:v>run_visual_magnifier_capture</x:v>
-      </x:c>
-      <x:c r="C3" s="8" t="str">
-        <x:v>Run visual.magnifier.capture</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="str">
-        <x:v>This form invokes only this MethodMesh capability. Inputs shown here are only those relevant to this call; capability interaction may continue in the native MethodMesh surface and return on Commit.</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="str">
+      <x:c r="B5" s="9" t="str">
+        <x:v>magnifier_capture</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>Inspect and capture with MethodMesh magnifier</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="str">
         <x:v>field-list</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str"/>
-      <x:c r="G3" s="8" t="str"/>
-      <x:c r="H3" s="8" t="str"/>
-      <x:c r="I3" s="8" t="str"/>
-      <x:c r="J3" s="8" t="str"/>
-      <x:c r="K3" s="8" t="str"/>
-      <x:c r="L3" s="8" t="str"/>
-      <x:c r="M3" s="8" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='visual.magnifier.capture',input_initial_zoom='2.0',input_default_filter='normal',input_allow_torch='true',input_payload_mode='FULL',return_mode='flat')</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="8" t="str">
-        <x:v>note</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="str">
-        <x:v>native_interaction</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="str">
-        <x:v>Complete the capability in MethodMesh, then Commit to return.</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="str">
-        <x:v>No undocumented ODK inputs have been invented for this showcase.</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str"/>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
-      <x:c r="L4" s="8" t="str"/>
-      <x:c r="M4" s="8" t="str"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+      <x:c r="E5" s="9" t="str"/>
+      <x:c r="F5" s="9" t="str">
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='visual.magnifier.capture',input_camera_facing=${camera_facing},input_initial_zoom='2.0',input_default_filter=${default_filter},input_allow_torch='true',input_allow_front_light='true',input_default_light=${default_light},input_front_light_brightness='1.0',input_payload_mode='FULL',return_mode='flat')</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
+        <x:v>image</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>magnifier_image_uri</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>Captured magnifier image</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="str"/>
+      <x:c r="E6" s="9" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F6" s="9" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>methodmesh_status</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
-        <x:v>Methodmesh Status</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="str">
-        <x:v>Shared MethodMesh transport status, where projected by the runtime.</x:v>
-      </x:c>
-      <x:c r="E5" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str"/>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
-      <x:c r="L5" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M5" s="8" t="str"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="8" t="str">
-        <x:v>image</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="str">
-        <x:v>magnifier_image_uri</x:v>
-      </x:c>
-      <x:c r="C6" s="8" t="str">
-        <x:v>Captured magnifier image</x:v>
-      </x:c>
-      <x:c r="D6" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E6" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str"/>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
-      <x:c r="L6" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M6" s="8" t="str"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="B7" s="9" t="str">
+        <x:v>magnifier_status</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>Magnifier status</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="str"/>
+      <x:c r="E7" s="9" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F7" s="9" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="9" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
-        <x:v>magnifier_status</x:v>
-      </x:c>
-      <x:c r="C7" s="8" t="str">
-        <x:v>Magnifier status</x:v>
-      </x:c>
-      <x:c r="D7" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E7" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str"/>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
-      <x:c r="L7" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M7" s="8" t="str"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="8" t="str">
+      <x:c r="B8" s="9" t="str">
+        <x:v>magnifier_image_sha256</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>Captured image SHA-256</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="str"/>
+      <x:c r="E8" s="9" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="9" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
-        <x:v>magnifier_image_sha256</x:v>
-      </x:c>
-      <x:c r="C8" s="8" t="str">
-        <x:v>Captured image SHA-256</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E8" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="str"/>
-      <x:c r="G8" s="8" t="str"/>
-      <x:c r="H8" s="8" t="str"/>
-      <x:c r="I8" s="8" t="str"/>
-      <x:c r="J8" s="8" t="str"/>
-      <x:c r="K8" s="8" t="str"/>
-      <x:c r="L8" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="str"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="8" t="str">
+      <x:c r="B9" s="9" t="str">
+        <x:v>magnifier_camera_facing</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>Camera used</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="str"/>
+      <x:c r="E9" s="9" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F9" s="9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="9" t="str">
         <x:v>text</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
+      <x:c r="B10" s="9" t="str">
+        <x:v>magnifier_filter_mode</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>Filter used</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="str"/>
+      <x:c r="E10" s="9" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F10" s="9" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="9" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="str">
+        <x:v>magnifier_torch_mode</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>Back light used</x:v>
+      </x:c>
+      <x:c r="D11" s="9" t="str"/>
+      <x:c r="E11" s="9" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F11" s="9" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="9" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="str">
+        <x:v>magnifier_front_light_mode</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>Front light used</x:v>
+      </x:c>
+      <x:c r="D12" s="9" t="str"/>
+      <x:c r="E12" s="9" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F12" s="9" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="9" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
         <x:v>methodmesh_full_json</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="C13" s="9" t="str">
         <x:v>MethodMesh audit metadata</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="str">
-        <x:v>Shared MethodMesh FULL execution envelope. Retained for complete execution/audit capture; capability-specific return fields are projected separately.</x:v>
-      </x:c>
-      <x:c r="E9" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F9" s="8" t="str"/>
-      <x:c r="G9" s="8" t="str"/>
-      <x:c r="H9" s="8" t="str"/>
-      <x:c r="I9" s="8" t="str"/>
-      <x:c r="J9" s="8" t="str"/>
-      <x:c r="K9" s="8" t="str"/>
-      <x:c r="L9" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M9" s="8" t="str"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="8" t="str">
+      <x:c r="D13" s="9" t="str"/>
+      <x:c r="E13" s="9" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="F13" s="9" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="9" t="str">
         <x:v>end_group</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str"/>
-      <x:c r="C10" s="8" t="str"/>
-      <x:c r="D10" s="8" t="str"/>
-      <x:c r="E10" s="8" t="str"/>
-      <x:c r="F10" s="8" t="str"/>
-      <x:c r="G10" s="8" t="str"/>
-      <x:c r="H10" s="8" t="str"/>
-      <x:c r="I10" s="8" t="str"/>
-      <x:c r="J10" s="8" t="str"/>
-      <x:c r="K10" s="8" t="str"/>
-      <x:c r="L10" s="8" t="str"/>
-      <x:c r="M10" s="8" t="str"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="8" t="str">
-        <x:v>note</x:v>
-      </x:c>
-      <x:c r="B11" s="8" t="str">
-        <x:v>return_summary</x:v>
-      </x:c>
-      <x:c r="C11" s="8" t="str">
-        <x:v>MethodMesh return captured. Status: ${methodmesh_status}</x:v>
-      </x:c>
-      <x:c r="D11" s="8" t="str">
-        <x:v>Only fields relevant to this capability are stored, plus the shared FULL envelope.</x:v>
-      </x:c>
-      <x:c r="E11" s="8" t="str"/>
-      <x:c r="F11" s="8" t="str"/>
-      <x:c r="G11" s="8" t="str"/>
-      <x:c r="H11" s="8" t="str"/>
-      <x:c r="I11" s="8" t="str"/>
-      <x:c r="J11" s="8" t="str"/>
-      <x:c r="K11" s="8" t="str"/>
-      <x:c r="L11" s="8" t="str"/>
-      <x:c r="M11" s="8" t="str"/>
+      <x:c r="B14" s="9" t="str"/>
+      <x:c r="C14" s="9" t="str"/>
+      <x:c r="D14" s="9" t="str"/>
+      <x:c r="E14" s="9" t="str"/>
+      <x:c r="F14" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -582,18 +544,117 @@
   <x:cols>
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>list_name</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="9" t="str">
+        <x:v>magnifier_camera</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>rear</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>Rear camera</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="9" t="str">
+        <x:v>magnifier_camera</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="str">
+        <x:v>front</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>Front camera</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>magnifier_light</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="str">
+        <x:v>off</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>magnifier_light</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="str">
+        <x:v>back</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>Back light</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
+        <x:v>magnifier_light</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="str">
+        <x:v>front</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>Front light</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
+        <x:v>magnifier_filter</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="str">
+        <x:v>normal</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="9" t="str">
+        <x:v>magnifier_filter</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="str">
+        <x:v>high_contrast</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>Contrast</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="9" t="str">
+        <x:v>magnifier_filter</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="str">
+        <x:v>monochrome</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>Mono</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="9" t="str">
+        <x:v>magnifier_filter</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="str">
+        <x:v>negative</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>Negative</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -605,31 +666,31 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>form_title</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>form_id</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>version</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>MethodMesh Magnifier — visual.magnifier.capture</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>magnifier_visual_magnifier_capture</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>2026090701</x:v>
+      <x:c r="A2" s="9" t="str">
+        <x:v>visual.magnifier.capture</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="str">
+        <x:v>visual_magnifier_capture_showcase</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>2026090803</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
